--- a/vch1101/files/kahoot/VCH1101_Kahoot_Unit1_textbook.xlsx
+++ b/vch1101/files/kahoot/VCH1101_Kahoot_Unit1_textbook.xlsx
@@ -717,25 +717,25 @@
       </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
+          <t>尊守</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>遵守</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
           <t>遵收</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
-        <is>
-          <t>尊守</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>遵守</t>
-        </is>
-      </c>
       <c r="G9" s="22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" s="1" t="n"/>
@@ -751,30 +751,30 @@
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
+          <t>幕門</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
           <t>暮門</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>墓門</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
-        <is>
-          <t>幕門</t>
-        </is>
-      </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
           <t>慕門</t>
         </is>
       </c>
       <c r="G10" s="25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H10" s="26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" s="1" t="n"/>
@@ -785,31 +785,31 @@
       </c>
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>課本錯別字表：「搔擾」嘅正字係邊個？</t>
+          <t>課本錯別字表：「振定」嘅正字係邊個？</t>
         </is>
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
-          <t>掃擾</t>
+          <t>振定</t>
         </is>
       </c>
       <c r="D11" s="25" t="inlineStr">
         <is>
-          <t>騷優</t>
+          <t>震定</t>
         </is>
       </c>
       <c r="E11" s="25" t="inlineStr">
         <is>
-          <t>搔擾</t>
+          <t>陣定</t>
         </is>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>騷擾</t>
+          <t>鎮定</t>
         </is>
       </c>
       <c r="G11" s="25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H11" s="26" t="inlineStr">
         <is>
@@ -824,31 +824,31 @@
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>課本餐牌上「美國茨條」，正確應該寫成？</t>
+          <t>課本餐牌Ａ餐寫「牛油麪飽」，改正欄嘅正確寫法係？</t>
         </is>
       </c>
       <c r="C12" s="25" t="inlineStr">
         <is>
-          <t>美國紫條</t>
+          <t>麪飽</t>
         </is>
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>美國薯條</t>
+          <t>麪包</t>
         </is>
       </c>
       <c r="E12" s="25" t="inlineStr">
         <is>
-          <t>美國茹條</t>
+          <t>麪苞</t>
         </is>
       </c>
       <c r="F12" s="25" t="inlineStr">
         <is>
-          <t>美國茨條</t>
+          <t>麪胞</t>
         </is>
       </c>
       <c r="G12" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H12" s="26" t="inlineStr">
         <is>
@@ -863,35 +863,35 @@
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>課本餐牌上「蘿白糕」，正確應該寫成？</t>
+          <t>課本餐牌Ｂ餐寫「火退通粉」，改正欄嘅正確寫法係？</t>
         </is>
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
-          <t>蘿北糕</t>
+          <t>火退</t>
         </is>
       </c>
       <c r="D13" s="25" t="inlineStr">
         <is>
-          <t>蘿蔔糕</t>
+          <t>火褪</t>
         </is>
       </c>
       <c r="E13" s="25" t="inlineStr">
         <is>
-          <t>蘿白糕</t>
+          <t>火腿</t>
         </is>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>羅蔔糕</t>
+          <t>火蛻</t>
         </is>
       </c>
       <c r="G13" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H13" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" s="1" t="n"/>
@@ -902,31 +902,31 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>課本話「以經」應寫成「已經」，呢個屬於邊一種寫錯別字嘅原因？</t>
+          <t>課本餐牌Ｄ餐寫「蘿白糕」，改正欄嘅正確寫法係？</t>
         </is>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
-          <t>把讀音相同或相似的字混淆</t>
+          <t>蘿蔔糕</t>
         </is>
       </c>
       <c r="D14" s="25" t="inlineStr">
         <is>
-          <t>部首寫錯</t>
+          <t>蘿白糕</t>
         </is>
       </c>
       <c r="E14" s="25" t="inlineStr">
         <is>
-          <t>錯誤理解詞義</t>
+          <t>蘿卜糕</t>
         </is>
       </c>
       <c r="F14" s="25" t="inlineStr">
         <is>
-          <t>把字形相似的字混淆</t>
+          <t>羅蔔糕</t>
         </is>
       </c>
       <c r="G14" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H14" s="26" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>課本話「重滔覆轍」應寫成「重蹈覆轍」，呢個屬於邊一種原因？</t>
+          <t>課本成因表：「以經」應寫成「已經」，「事非」應寫成「是非」。呢類錯別字屬於邊一種成因？</t>
         </is>
       </c>
       <c r="C15" s="25" t="inlineStr">
@@ -951,21 +951,21 @@
       </c>
       <c r="D15" s="25" t="inlineStr">
         <is>
-          <t>漏寫標點</t>
+          <t>把字形相似的字混淆</t>
         </is>
       </c>
       <c r="E15" s="25" t="inlineStr">
         <is>
+          <t>書寫態度不夠認真</t>
+        </is>
+      </c>
+      <c r="F15" s="25" t="inlineStr">
+        <is>
           <t>把讀音相同或相似的字混淆</t>
         </is>
       </c>
-      <c r="F15" s="25" t="inlineStr">
-        <is>
-          <t>把字形相似的字混淆</t>
-        </is>
-      </c>
       <c r="G15" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H15" s="26" t="inlineStr">
         <is>
@@ -980,31 +980,31 @@
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>課本話「助慶」應寫成「助興」，呢個屬於邊一種原因？</t>
+          <t>課本成因表：「重滔覆轍」應寫成「重蹈覆轍」。課本話「蹈」係咩意思，所以要用「蹈」？</t>
         </is>
       </c>
       <c r="C16" s="25" t="inlineStr">
         <is>
-          <t>把字形相似的字混淆</t>
+          <t>大水滾滾不絕</t>
         </is>
       </c>
       <c r="D16" s="25" t="inlineStr">
         <is>
-          <t>錯誤理解詞義</t>
+          <t>踏</t>
         </is>
       </c>
       <c r="E16" s="25" t="inlineStr">
         <is>
-          <t>把讀音相同或相似的字混淆</t>
+          <t>重複</t>
         </is>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>筆順寫錯</t>
+          <t>到達</t>
         </is>
       </c>
       <c r="G16" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H16" s="26" t="inlineStr">
         <is>
@@ -1019,35 +1019,35 @@
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>課本練習：「篇寫」應該改正為？</t>
+          <t>課本成因表：「助慶」應寫成「助興」，「不知所蹤」應寫成「不知所終」。呢類錯別字屬於邊一種成因？</t>
         </is>
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
-          <t>篇寫</t>
+          <t>把字形相似的字混淆</t>
         </is>
       </c>
       <c r="D17" s="25" t="inlineStr">
         <is>
-          <t>編寫</t>
+          <t>把讀音相同或相似的字混淆</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
         <is>
-          <t>偏寫</t>
+          <t>錯誤理解詞義</t>
         </is>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>遍寫</t>
+          <t>不懂得分辨詞性</t>
         </is>
       </c>
       <c r="G17" s="25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H17" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I17" s="1" t="n"/>
@@ -1058,35 +1058,35 @@
       </c>
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>課本練習：「籃色」應該改正為？</t>
+          <t>課本便條：「會計部急須取用鉛筆一打、籃色圓珠筆兩打、記事薄五本」。以下邊個改正完全正確？</t>
         </is>
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
-          <t>籃色</t>
+          <t>急需、藍色、記事簿</t>
         </is>
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>藍色</t>
+          <t>急須、籃色、記事簿</t>
         </is>
       </c>
       <c r="E18" s="25" t="inlineStr">
         <is>
-          <t>檻色</t>
+          <t>急需、籃色、記事簿</t>
         </is>
       </c>
       <c r="F18" s="25" t="inlineStr">
         <is>
-          <t>覽色</t>
+          <t>急需、藍色、記事薄</t>
         </is>
       </c>
       <c r="G18" s="25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H18" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I18" s="1" t="n"/>
@@ -1097,35 +1097,35 @@
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>課本便條：「記事薄五本」嘅「薄」應該改正為？</t>
+          <t>課本超市特價單寫「車箱香精座」。「車箱」應改正為？</t>
         </is>
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
-          <t>布</t>
+          <t>車箱</t>
         </is>
       </c>
       <c r="D19" s="25" t="inlineStr">
         <is>
-          <t>部</t>
+          <t>車相</t>
         </is>
       </c>
       <c r="E19" s="25" t="inlineStr">
         <is>
-          <t>簿</t>
+          <t>車湘</t>
         </is>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>薄</t>
+          <t>車廂</t>
         </is>
       </c>
       <c r="G19" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H19" s="26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I19" s="1" t="n"/>
@@ -1136,35 +1136,35 @@
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>課本徵聘廣告：「要求侍遇」嘅「侍」應該改正為？</t>
+          <t>課本旅行團單張寫「特別按排住宿一晚新加坡」。「按排」應改正為？</t>
         </is>
       </c>
       <c r="C20" s="25" t="inlineStr">
         <is>
-          <t>持</t>
+          <t>按排</t>
         </is>
       </c>
       <c r="D20" s="25" t="inlineStr">
         <is>
-          <t>恃</t>
+          <t>安排</t>
         </is>
       </c>
       <c r="E20" s="25" t="inlineStr">
         <is>
-          <t>待</t>
+          <t>案排</t>
         </is>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>侍</t>
+          <t>岸排</t>
         </is>
       </c>
       <c r="G20" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H20" s="26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" s="1" t="n"/>
@@ -1175,35 +1175,35 @@
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>課本超市特價單：「嗽口水」嘅「嗽」應該改正為？</t>
+          <t>課本故事：「僕人聽了一聲不坑地拿著盒子出去」。「坑」應改正為？</t>
         </is>
       </c>
       <c r="C21" s="25" t="inlineStr">
         <is>
-          <t>嫩</t>
+          <t>吭</t>
         </is>
       </c>
       <c r="D21" s="25" t="inlineStr">
         <is>
-          <t>敕</t>
+          <t>坑</t>
         </is>
       </c>
       <c r="E21" s="25" t="inlineStr">
         <is>
-          <t>漱</t>
+          <t>亢</t>
         </is>
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>嗽</t>
+          <t>抗</t>
         </is>
       </c>
       <c r="G21" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H21" s="26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I21" s="1" t="n"/>
@@ -1214,35 +1214,35 @@
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>課本超市特價單：「車箱香精座」嘅「箱」應該改正為？</t>
+          <t>課本故事：「僕人感到莫明其妙」。「明」應改正為？</t>
         </is>
       </c>
       <c r="C22" s="25" t="inlineStr">
         <is>
-          <t>相</t>
+          <t>明</t>
         </is>
       </c>
       <c r="D22" s="25" t="inlineStr">
         <is>
-          <t>廂</t>
+          <t>銘</t>
         </is>
       </c>
       <c r="E22" s="25" t="inlineStr">
         <is>
-          <t>箱</t>
+          <t>名</t>
         </is>
       </c>
       <c r="F22" s="25" t="inlineStr">
         <is>
-          <t>湘</t>
+          <t>鳴</t>
         </is>
       </c>
       <c r="G22" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H22" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I22" s="1" t="n"/>
@@ -1253,31 +1253,31 @@
       </c>
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>課本旅行團單張：「特別安排沙莫之旅」嘅「莫」應該改正為？</t>
+          <t>課本故事：「老夫人就大發雷庭」。「庭」應改正為？</t>
         </is>
       </c>
       <c r="C23" s="25" t="inlineStr">
         <is>
-          <t>寞</t>
+          <t>庭</t>
         </is>
       </c>
       <c r="D23" s="25" t="inlineStr">
         <is>
-          <t>漠</t>
+          <t>霆</t>
         </is>
       </c>
       <c r="E23" s="25" t="inlineStr">
         <is>
-          <t>莫</t>
+          <t>廷</t>
         </is>
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>幕</t>
+          <t>蜓</t>
         </is>
       </c>
       <c r="G23" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H23" s="26" t="inlineStr">
         <is>
@@ -1292,35 +1292,35 @@
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>課本故事：「就大發雷庭」嘅「庭」應該改正為？</t>
+          <t>課本話「冷 ─ 暖 ─ 熱」呢一組係邊一類詞？</t>
         </is>
       </c>
       <c r="C24" s="25" t="inlineStr">
         <is>
-          <t>霆</t>
+          <t>近義詞</t>
         </is>
       </c>
       <c r="D24" s="25" t="inlineStr">
         <is>
-          <t>庭</t>
+          <t>絕對反義詞</t>
         </is>
       </c>
       <c r="E24" s="25" t="inlineStr">
         <is>
-          <t>廷</t>
+          <t>等義詞</t>
         </is>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>蜓</t>
+          <t>相對反義詞</t>
         </is>
       </c>
       <c r="G24" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H24" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I24" s="1" t="n"/>
@@ -1331,35 +1331,35 @@
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>課本故事：「僕人聽了一聲不坑地拿著盒子出去」嘅「坑」應該改正為？</t>
+          <t>課本表格將「出席」同「缺席」歸入邊一類？</t>
         </is>
       </c>
       <c r="C25" s="25" t="inlineStr">
         <is>
-          <t>抗</t>
+          <t>絕對反義詞</t>
         </is>
       </c>
       <c r="D25" s="25" t="inlineStr">
         <is>
-          <t>亢</t>
+          <t>相對反義詞</t>
         </is>
       </c>
       <c r="E25" s="25" t="inlineStr">
         <is>
-          <t>坑</t>
+          <t>等義詞</t>
         </is>
       </c>
       <c r="F25" s="25" t="inlineStr">
         <is>
-          <t>吭</t>
+          <t>近義詞</t>
         </is>
       </c>
       <c r="G25" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H25" s="26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I25" s="1" t="n"/>
@@ -1370,31 +1370,31 @@
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>課本話「冷 ── 暖 ── 熱」呢一組屬於邊一類？</t>
+          <t>課本列舉等義詞嘅例子係邊一組？</t>
         </is>
       </c>
       <c r="C26" s="25" t="inlineStr">
         <is>
-          <t>近義詞</t>
+          <t>破除／消除／解除</t>
         </is>
       </c>
       <c r="D26" s="25" t="inlineStr">
         <is>
-          <t>相對反義詞</t>
+          <t>母親／媽媽／娘</t>
         </is>
       </c>
       <c r="E26" s="25" t="inlineStr">
         <is>
-          <t>絕對反義詞</t>
+          <t>冷／暖／熱</t>
         </is>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>等義詞</t>
+          <t>臨渴掘井／未雨綢繆</t>
         </is>
       </c>
       <c r="G26" s="25" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H26" s="26" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>課本題目：「沒有經過討論，陳經理就下了取消交通津貼的決定，真是太草率了。」「草率」嘅反義詞係？</t>
+          <t>課本題：「沒有經過討論，陳經理就下了取消交通津貼的決定，真是太草率了。」「草率」嘅反義詞係？</t>
         </is>
       </c>
       <c r="C27" s="25" t="inlineStr">
@@ -1419,21 +1419,21 @@
       </c>
       <c r="D27" s="25" t="inlineStr">
         <is>
+          <t>熱衷</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
+        <is>
+          <t>認真</t>
+        </is>
+      </c>
+      <c r="F27" s="25" t="inlineStr">
+        <is>
           <t>懶惰</t>
         </is>
       </c>
-      <c r="E27" s="25" t="inlineStr">
-        <is>
-          <t>認真</t>
-        </is>
-      </c>
-      <c r="F27" s="25" t="inlineStr">
-        <is>
-          <t>熱衷</t>
-        </is>
-      </c>
       <c r="G27" s="25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H27" s="26" t="inlineStr">
         <is>
@@ -1448,35 +1448,35 @@
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>課本練習：「遵守」嘅反義詞係邊個？</t>
+          <t>課本題：「交流電在電子學中扮演重要的角色，它的應用範圍比直流電更廣泛。」「廣泛」嘅同義詞係？</t>
         </is>
       </c>
       <c r="C28" s="25" t="inlineStr">
         <is>
-          <t>執行</t>
+          <t>狹窄</t>
         </is>
       </c>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>聽從</t>
+          <t>隨便</t>
         </is>
       </c>
       <c r="E28" s="25" t="inlineStr">
         <is>
-          <t>違反</t>
+          <t>遙遠</t>
         </is>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>規矩</t>
+          <t>普遍</t>
         </is>
       </c>
       <c r="G28" s="25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H28" s="26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I28" s="1" t="n"/>
@@ -1487,31 +1487,31 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>課本挑戰站：妹妹去澳洲升學這件事必須（　）</t>
+          <t>課本題：「防煙門的功能是＿＿煙火的蔓延。」應該填邊個詞？</t>
         </is>
       </c>
       <c r="C29" s="27" t="inlineStr">
         <is>
-          <t>從長計議</t>
+          <t>阻止</t>
         </is>
       </c>
       <c r="D29" s="27" t="inlineStr">
         <is>
-          <t>從詳計議</t>
+          <t>妨礙</t>
         </is>
       </c>
       <c r="E29" s="27" t="inlineStr">
         <is>
-          <t>從詳計畫</t>
+          <t>阻礙</t>
         </is>
       </c>
       <c r="F29" s="27" t="inlineStr">
         <is>
-          <t>從長計議論</t>
+          <t>障礙</t>
         </is>
       </c>
       <c r="G29" s="25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H29" s="28" t="inlineStr">
         <is>

--- a/vch1101/files/kahoot/VCH1101_Kahoot_Unit1_textbook.xlsx
+++ b/vch1101/files/kahoot/VCH1101_Kahoot_Unit1_textbook.xlsx
@@ -1487,27 +1487,27 @@
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>課本題：「防煙門的功能是＿＿煙火的蔓延。」應該填邊個詞？</t>
+          <t>課本題：「經過多年努力，他的事業已經有了＿＿。」應該填邊個詞？</t>
         </is>
       </c>
       <c r="C29" s="27" t="inlineStr">
         <is>
-          <t>阻止</t>
+          <t>結果</t>
         </is>
       </c>
       <c r="D29" s="27" t="inlineStr">
         <is>
-          <t>妨礙</t>
+          <t>成果</t>
         </is>
       </c>
       <c r="E29" s="27" t="inlineStr">
         <is>
-          <t>阻礙</t>
+          <t>效果</t>
         </is>
       </c>
       <c r="F29" s="27" t="inlineStr">
         <is>
-          <t>障礙</t>
+          <t>後果</t>
         </is>
       </c>
       <c r="G29" s="25" t="n">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="H29" s="28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I29" s="1" t="n"/>
